--- a/01_用AI生成Excel/05_邏輯判斷/業績獎金判定.xlsx
+++ b/01_用AI生成Excel/05_邏輯判斷/業績獎金判定.xlsx
@@ -163,10 +163,18 @@
     <tableColumn id="4" name="業績目標"/>
     <tableColumn id="5" name="實際業績"/>
     <tableColumn id="6" name="全勤"/>
-    <tableColumn id="7" name="達成率"/>
-    <tableColumn id="8" name="是否達標"/>
-    <tableColumn id="9" name="獎金等級"/>
-    <tableColumn id="10" name="全勤加碼"/>
+    <tableColumn id="7" name="達成率">
+      <calculatedColumnFormula>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="8" name="是否達標">
+      <calculatedColumnFormula>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="9" name="獎金等級">
+      <calculatedColumnFormula>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</calculatedColumnFormula>
+    </tableColumn>
+    <tableColumn id="10" name="全勤加碼">
+      <calculatedColumnFormula>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</calculatedColumnFormula>
+    </tableColumn>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showRowStripes="1"/>
 </table>
@@ -556,19 +564,19 @@
         </is>
       </c>
       <c r="G2" s="4">
-        <f>E2/D2</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H2" s="2">
-        <f>IF(G2&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I2" s="2">
-        <f>_xlfn.IFS(G2&gt;='獎金規則'!$B$2,"A",G2&gt;='獎金規則'!$B$3,"B",G2&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J2" s="2">
-        <f>IF(AND(H2="達標",F2="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -600,19 +608,19 @@
         </is>
       </c>
       <c r="G3" s="4">
-        <f>E3/D3</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H3" s="2">
-        <f>IF(G3&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I3" s="2">
-        <f>_xlfn.IFS(G3&gt;='獎金規則'!$B$2,"A",G3&gt;='獎金規則'!$B$3,"B",G3&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J3" s="2">
-        <f>IF(AND(H3="達標",F3="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -644,19 +652,19 @@
         </is>
       </c>
       <c r="G4" s="4">
-        <f>E4/D4</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H4" s="2">
-        <f>IF(G4&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I4" s="2">
-        <f>_xlfn.IFS(G4&gt;='獎金規則'!$B$2,"A",G4&gt;='獎金規則'!$B$3,"B",G4&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J4" s="2">
-        <f>IF(AND(H4="達標",F4="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -688,19 +696,19 @@
         </is>
       </c>
       <c r="G5" s="4">
-        <f>E5/D5</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H5" s="2">
-        <f>IF(G5&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I5" s="2">
-        <f>_xlfn.IFS(G5&gt;='獎金規則'!$B$2,"A",G5&gt;='獎金規則'!$B$3,"B",G5&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J5" s="2">
-        <f>IF(AND(H5="達標",F5="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -732,19 +740,19 @@
         </is>
       </c>
       <c r="G6" s="4">
-        <f>E6/D6</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H6" s="2">
-        <f>IF(G6&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I6" s="2">
-        <f>_xlfn.IFS(G6&gt;='獎金規則'!$B$2,"A",G6&gt;='獎金規則'!$B$3,"B",G6&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J6" s="2">
-        <f>IF(AND(H6="達標",F6="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -776,19 +784,19 @@
         </is>
       </c>
       <c r="G7" s="4">
-        <f>E7/D7</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H7" s="2">
-        <f>IF(G7&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I7" s="2">
-        <f>_xlfn.IFS(G7&gt;='獎金規則'!$B$2,"A",G7&gt;='獎金規則'!$B$3,"B",G7&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J7" s="2">
-        <f>IF(AND(H7="達標",F7="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -820,19 +828,19 @@
         </is>
       </c>
       <c r="G8" s="4">
-        <f>E8/D8</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H8" s="2">
-        <f>IF(G8&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I8" s="2">
-        <f>_xlfn.IFS(G8&gt;='獎金規則'!$B$2,"A",G8&gt;='獎金規則'!$B$3,"B",G8&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J8" s="2">
-        <f>IF(AND(H8="達標",F8="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -864,19 +872,19 @@
         </is>
       </c>
       <c r="G9" s="4">
-        <f>E9/D9</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H9" s="2">
-        <f>IF(G9&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I9" s="2">
-        <f>_xlfn.IFS(G9&gt;='獎金規則'!$B$2,"A",G9&gt;='獎金規則'!$B$3,"B",G9&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J9" s="2">
-        <f>IF(AND(H9="達標",F9="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -908,19 +916,19 @@
         </is>
       </c>
       <c r="G10" s="4">
-        <f>E10/D10</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H10" s="2">
-        <f>IF(G10&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I10" s="2">
-        <f>_xlfn.IFS(G10&gt;='獎金規則'!$B$2,"A",G10&gt;='獎金規則'!$B$3,"B",G10&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J10" s="2">
-        <f>IF(AND(H10="達標",F10="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -952,19 +960,19 @@
         </is>
       </c>
       <c r="G11" s="4">
-        <f>E11/D11</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H11" s="2">
-        <f>IF(G11&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I11" s="2">
-        <f>_xlfn.IFS(G11&gt;='獎金規則'!$B$2,"A",G11&gt;='獎金規則'!$B$3,"B",G11&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J11" s="2">
-        <f>IF(AND(H11="達標",F11="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -996,19 +1004,19 @@
         </is>
       </c>
       <c r="G12" s="4">
-        <f>E12/D12</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H12" s="2">
-        <f>IF(G12&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I12" s="2">
-        <f>_xlfn.IFS(G12&gt;='獎金規則'!$B$2,"A",G12&gt;='獎金規則'!$B$3,"B",G12&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J12" s="2">
-        <f>IF(AND(H12="達標",F12="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
@@ -1040,19 +1048,19 @@
         </is>
       </c>
       <c r="G13" s="4">
-        <f>E13/D13</f>
+        <f>T_Bonus[[#This Row],[實際業績]]/T_Bonus[[#This Row],[業績目標]]</f>
         <v/>
       </c>
       <c r="H13" s="2">
-        <f>IF(G13&gt;='獎金規則'!$B$3,"達標","未達標")</f>
+        <f>IF(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"達標","未達標")</f>
         <v/>
       </c>
       <c r="I13" s="2">
-        <f>_xlfn.IFS(G13&gt;='獎金規則'!$B$2,"A",G13&gt;='獎金規則'!$B$3,"B",G13&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
+        <f>_xlfn.IFS(T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$2,"A",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$3,"B",T_Bonus[[#This Row],[達成率]]&gt;='獎金規則'!$B$4,"C",TRUE,"無")</f>
         <v/>
       </c>
       <c r="J13" s="2">
-        <f>IF(AND(H13="達標",F13="是"),"是","否")</f>
+        <f>IF(AND(T_Bonus[[#This Row],[是否達標]]="達標",T_Bonus[[#This Row],[全勤]]="是"),"是","否")</f>
         <v/>
       </c>
     </row>
